--- a/Calibration_UWB/Erreur_UWB_2.xlsx
+++ b/Calibration_UWB/Erreur_UWB_2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{0F16DEF9-574B-49E9-86F9-4885D618C529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{3432B3F7-2079-4B90-A4C0-F53B175D63F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3432B3F7-2079-4B90-A4C0-F53B175D63F2}"/>
   </bookViews>
   <sheets>
     <sheet name="UWB_horizontale" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="UWB_drone_face_face" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -181,14 +180,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -199,11 +192,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2279,63 +2274,63 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="I2" s="3" t="s">
+      <c r="G2" s="6"/>
+      <c r="I2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="4">
+      <c r="B3" s="6">
         <v>120</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6">
         <v>120</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
+      <c r="B4" s="6">
         <v>130</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6">
         <v>132.4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="I4" s="3" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
+      <c r="B5" s="6">
         <v>140</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6">
         <v>143.6</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2344,16 +2339,16 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
+      <c r="B6" s="6">
         <v>150</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6">
         <v>154.19999999999999</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
       <c r="I6" s="1">
         <v>-4</v>
       </c>
@@ -2362,130 +2357,130 @@
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>160</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6">
         <v>165.7</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
+      <c r="B8" s="6">
         <v>170</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6">
         <v>176.4</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="4">
+      <c r="B9" s="6">
         <v>110</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6">
         <v>110.6</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="4">
+      <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6">
         <v>100</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>90</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6">
         <v>89.2</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="4">
+      <c r="B12" s="6">
         <v>80</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6">
         <v>78</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
+      <c r="B13" s="6">
         <v>70</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6">
         <v>67</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4" t="s">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="4"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="4">
+      <c r="B17" s="6">
         <v>120</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6">
         <v>119.6</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="I17" s="3" t="s">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="I17" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="4">
+      <c r="B18" s="6">
         <v>130</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6">
         <v>130</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
       <c r="I18" s="1" t="s">
         <v>9</v>
       </c>
@@ -2494,16 +2489,16 @@
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="4">
+      <c r="B19" s="6">
         <v>140</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6">
         <v>140</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
       <c r="I19" s="1">
         <v>4</v>
       </c>
@@ -2512,109 +2507,156 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="4">
+      <c r="B20" s="6">
         <v>150</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6">
         <v>152.69999999999999</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="4">
+      <c r="B21" s="6">
         <v>160</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6">
         <v>162</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="4">
+      <c r="B22" s="6">
         <v>170</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4">
+      <c r="C22" s="6"/>
+      <c r="D22" s="6">
         <v>172.2</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="4">
+      <c r="B23" s="6">
         <v>110</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4">
+      <c r="C23" s="6"/>
+      <c r="D23" s="6">
         <v>108.2</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="4">
+      <c r="B24" s="6">
         <v>100</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4">
+      <c r="C24" s="6"/>
+      <c r="D24" s="6">
         <v>97.4</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="4">
+      <c r="B25" s="6">
         <v>90</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4">
+      <c r="C25" s="6"/>
+      <c r="D25" s="6">
         <v>85.6</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="4">
+      <c r="B26" s="6">
         <v>80</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4">
+      <c r="C26" s="6"/>
+      <c r="D26" s="6">
         <v>76.2</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="4">
+      <c r="B27" s="6">
         <v>70</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6">
         <v>64</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
@@ -2631,59 +2673,12 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2695,189 +2690,189 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>120</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6">
         <v>152</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>130</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
         <v>161.6</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>140</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
         <v>177.2</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>150</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>188</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="4">
+      <c r="C8" s="6">
         <v>160</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
         <v>192.2</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="4">
+      <c r="C9" s="6">
         <v>170</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
         <v>208.8</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="4">
+      <c r="C10" s="6">
         <v>110</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6">
         <v>143.5</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="4">
+      <c r="C11" s="6">
         <v>100</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
         <v>133.30000000000001</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="4">
+      <c r="C12" s="6">
         <v>90</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
         <v>122.8</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="4">
+      <c r="C13" s="6">
         <v>80</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
         <v>109.8</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="4">
+      <c r="C14" s="6">
         <v>70</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6">
         <v>97</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2894,24 +2889,24 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -2921,218 +2916,218 @@
         <f>ASIN(B6/120)*(180/PI())</f>
         <v>0</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="6">
         <v>120</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6">
         <v>117</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>10</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <f t="shared" ref="C7:C13" si="0">ASIN(B7/120)*(180/PI())</f>
         <v>4.7801918471991582</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="6">
         <v>121</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
         <v>118.4</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>20</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <f>ASIN(B8/120)*(180/PI())</f>
         <v>9.5940682268604629</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="6">
         <v>121.5</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6">
         <v>118.9</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>30</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>14.477512185929925</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="6">
         <v>122.5</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6">
         <v>119.1</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>40</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <f t="shared" si="0"/>
         <v>19.471220634490692</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="6">
         <v>125.8</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6">
         <v>124.8</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>50</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <f t="shared" si="0"/>
         <v>24.624318352164078</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="6">
         <v>128.5</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6">
         <v>128.69999999999999</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>60</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <f t="shared" si="0"/>
         <v>30.000000000000004</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="6">
         <v>132.5</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6">
         <v>134.4</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>70</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <f t="shared" si="0"/>
         <v>35.685334712652057</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="6">
         <v>137</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6">
         <v>142.6</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3144,243 +3139,242 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="7"/>
       <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="8"/>
+      <c r="B4" s="1"/>
       <c r="C4" s="2">
         <v>10</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="6">
         <v>120</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6">
         <v>116.7</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
-      <c r="C5" s="9">
+      <c r="B5" s="1"/>
+      <c r="C5" s="5">
         <v>20</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="6">
         <v>120</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="E5" s="6"/>
+      <c r="F5" s="6">
         <v>118.4</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="8"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="2">
         <v>30</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="6">
         <v>120</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6">
         <v>119.5</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="8"/>
-      <c r="C7" s="9">
+      <c r="B7" s="1"/>
+      <c r="C7" s="5">
         <v>40</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="6">
         <v>120</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
         <v>122.8</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="8"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="2">
         <v>50</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="6">
         <v>120</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6">
         <v>125.9</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9">
+      <c r="B9" s="1"/>
+      <c r="C9" s="5">
         <v>60</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="6">
         <v>120</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6">
         <v>124.2</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="8"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="2">
         <v>70</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="6">
         <v>120</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6">
         <v>123</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="8"/>
-      <c r="C11" s="9">
+      <c r="B11" s="1"/>
+      <c r="C11" s="5">
         <v>80</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="6">
         <v>120</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6">
         <v>124</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C12" s="2">
         <v>90</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="6">
         <v>120</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="10">
+      <c r="E12" s="6"/>
+      <c r="F12" s="8">
         <v>130</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="11"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="9"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4" t="s">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="6">
         <v>120</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6">
         <v>143.9</v>
       </c>
-      <c r="G16" s="4"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="6">
         <v>120</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6">
         <v>139.4</v>
       </c>
-      <c r="G17" s="4"/>
+      <c r="G17" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3392,165 +3386,165 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>120</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6">
         <v>115</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>110</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
         <v>104.3</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>100</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
         <v>92.6</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>130</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>124.1</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="4">
+      <c r="C8" s="6">
         <v>140</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
         <v>134.6</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calibration_UWB/Erreur_UWB_2.xlsx
+++ b/Calibration_UWB/Erreur_UWB_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Noé\Documents\GE5\Projet_SIoT\Projet-S-IoT-Essaim-de-Drone\Calibration_UWB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liene\Documents\INSA\S9\Projet S-IoT\Projet-S-IoT-Essaim-de-Drone\Calibration_UWB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{0F16DEF9-574B-49E9-86F9-4885D618C529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3956946C-4118-4A07-A0D5-0017D935A8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3432B3F7-2079-4B90-A4C0-F53B175D63F2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{3432B3F7-2079-4B90-A4C0-F53B175D63F2}"/>
   </bookViews>
   <sheets>
     <sheet name="UWB_horizontale" sheetId="1" r:id="rId1"/>
@@ -73,13 +73,7 @@
     <t xml:space="preserve">Erreur </t>
   </si>
   <si>
-    <t>UWB (2)</t>
-  </si>
-  <si>
     <t>Reference tick</t>
-  </si>
-  <si>
-    <t>UWB (Tag)</t>
   </si>
   <si>
     <t>Remarque : erreur dérive dans le temps</t>
@@ -104,6 +98,12 @@
   </si>
   <si>
     <t>opposé</t>
+  </si>
+  <si>
+    <t>UWB-1</t>
+  </si>
+  <si>
+    <t>UWB-3</t>
   </si>
 </sst>
 </file>
@@ -195,10 +195,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1578,9 +1578,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D655F8-00C4-4040-9A36-903A51E0E8F1}">
   <dimension ref="B1:J42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B2" s="1">
         <v>69.400000000000006</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>-50.599999999999994</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" s="1">
         <v>82.6</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>-37.400000000000006</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1">
         <v>91</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="1">
         <v>100</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" s="1">
         <v>107.3</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>-12.700000000000003</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="1">
         <v>120.5</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="1">
         <v>132</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <v>147.4</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>27.400000000000006</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="1">
         <v>155.5</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="1">
         <v>164.7</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>44.699999999999989</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="1">
         <v>167</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="1">
         <v>176</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B14" s="1">
         <v>189.6</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>69.599999999999994</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B15" s="1">
         <v>125</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="1">
         <v>130</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <v>135</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B18" s="1">
         <v>140</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B19" s="1">
         <v>145</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="1">
         <v>150</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" s="1">
         <v>155</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B22" s="1">
         <v>160</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B23" s="1">
         <v>165</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B24" s="1">
         <v>170</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B25" s="1">
         <v>175</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B26" s="1">
         <v>180</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B27" s="1">
         <v>185</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B28" s="1">
         <v>190</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B29" s="1">
         <v>115</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B30" s="1">
         <v>110</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B31" s="1">
         <v>105</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B32" s="1">
         <v>100</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B33" s="1">
         <v>95</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="1">
         <v>90</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="1">
         <v>85</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B36" s="1">
         <v>80</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B37" s="1">
         <v>75</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B38" s="1">
         <v>70</v>
       </c>
@@ -2250,16 +2250,16 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B42" s="1"/>
     </row>
   </sheetData>
@@ -2271,339 +2271,398 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE1F7BC-FE29-4E39-9FC1-2957A9FA7F3E}">
   <dimension ref="B2:K27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="I2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
+      <c r="G2" s="7"/>
+      <c r="I2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B3" s="7">
         <v>120</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7">
         <v>120</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="6">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B4" s="7">
         <v>130</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7">
         <v>132.4</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="I4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="6">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="I4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B5" s="7">
         <v>140</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7">
         <v>143.6</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
       <c r="I5" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B6" s="7">
         <v>150</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7">
         <v>154.19999999999999</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
       <c r="I6" s="1">
         <v>-4</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B7" s="7">
         <v>160</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6">
+      <c r="C7" s="7"/>
+      <c r="D7" s="7">
         <v>165.7</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="6">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B8" s="7">
         <v>170</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7">
         <v>176.4</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B9" s="7">
         <v>110</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7">
         <v>110.6</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="6">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B10" s="7">
         <v>100</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7">
         <v>100</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="6">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B11" s="7">
         <v>90</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7">
         <v>89.2</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="6">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B12" s="7">
         <v>80</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7">
         <v>78</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="6">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B13" s="7">
         <v>70</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7">
         <v>67</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="6" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="s">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="6">
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B17" s="7">
         <v>120</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7">
         <v>119.6</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="I17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="6">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B18" s="7">
         <v>130</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7">
         <v>130</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
       <c r="I18" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B19" s="7">
         <v>140</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7">
         <v>140</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
       <c r="I19" s="1">
         <v>4</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B20" s="7">
         <v>150</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7">
         <v>152.69999999999999</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="6">
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B21" s="7">
         <v>160</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7">
         <v>162</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="6">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B22" s="7">
         <v>170</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6">
+      <c r="C22" s="7"/>
+      <c r="D22" s="7">
         <v>172.2</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="6">
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B23" s="7">
         <v>110</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7">
         <v>108.2</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="6">
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B24" s="7">
         <v>100</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6">
+      <c r="C24" s="7"/>
+      <c r="D24" s="7">
         <v>97.4</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="6">
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B25" s="7">
         <v>90</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6">
+      <c r="C25" s="7"/>
+      <c r="D25" s="7">
         <v>85.6</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="6">
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B26" s="7">
         <v>80</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6">
+      <c r="C26" s="7"/>
+      <c r="D26" s="7">
         <v>76.2</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="6">
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B27" s="7">
         <v>70</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7">
         <v>64</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="75">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D26:E26"/>
@@ -2620,65 +2679,6 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2687,192 +2687,192 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{918B5849-25F8-49BF-97EF-C05F41F2E165}">
   <dimension ref="C3:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C3" s="6" t="s">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C4" s="6">
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C4" s="7">
         <v>120</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7">
         <v>152</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" s="6">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C5" s="7">
         <v>130</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7">
         <v>161.6</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="6">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C6" s="7">
         <v>140</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7">
         <v>177.2</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="6">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C7" s="7">
         <v>150</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7">
         <v>188</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="6">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C8" s="7">
         <v>160</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7">
         <v>192.2</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="6">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C9" s="7">
         <v>170</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7">
         <v>208.8</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="6">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C10" s="7">
         <v>110</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7">
         <v>143.5</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="6">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C11" s="7">
         <v>100</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7">
         <v>133.30000000000001</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="6">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C12" s="7">
         <v>90</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7">
         <v>122.8</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="6">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C13" s="7">
         <v>80</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7">
         <v>109.8</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="6">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C14" s="7">
         <v>70</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7">
         <v>97</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,34 +2881,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2538041D-3A3E-441C-B27A-5E9DF12E79A0}">
   <dimension ref="B5:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1328125" customWidth="1"/>
+    <col min="3" max="3" width="13.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B6" s="2">
         <v>0</v>
       </c>
@@ -2916,18 +2916,18 @@
         <f>ASIN(B6/120)*(180/PI())</f>
         <v>0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>120</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7">
         <v>117</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B7" s="2">
         <v>10</v>
       </c>
@@ -2935,18 +2935,18 @@
         <f t="shared" ref="C7:C13" si="0">ASIN(B7/120)*(180/PI())</f>
         <v>4.7801918471991582</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>121</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7">
         <v>118.4</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B8" s="2">
         <v>20</v>
       </c>
@@ -2954,18 +2954,18 @@
         <f>ASIN(B8/120)*(180/PI())</f>
         <v>9.5940682268604629</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>121.5</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7">
         <v>118.9</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B9" s="2">
         <v>30</v>
       </c>
@@ -2973,18 +2973,18 @@
         <f t="shared" si="0"/>
         <v>14.477512185929925</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>122.5</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7">
         <v>119.1</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B10" s="2">
         <v>40</v>
       </c>
@@ -2992,18 +2992,18 @@
         <f t="shared" si="0"/>
         <v>19.471220634490692</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>125.8</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7">
         <v>124.8</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B11" s="2">
         <v>50</v>
       </c>
@@ -3011,18 +3011,18 @@
         <f t="shared" si="0"/>
         <v>24.624318352164078</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>128.5</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7">
         <v>128.69999999999999</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B12" s="2">
         <v>60</v>
       </c>
@@ -3030,18 +3030,18 @@
         <f t="shared" si="0"/>
         <v>30.000000000000004</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>132.5</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7">
         <v>134.4</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B13" s="2">
         <v>70</v>
       </c>
@@ -3049,85 +3049,85 @@
         <f t="shared" si="0"/>
         <v>35.685334712652057</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>137</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7">
         <v>142.6</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3136,161 +3136,161 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E23074FB-E110-416C-914F-4412D44840BD}">
   <dimension ref="B3:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B4" s="1"/>
       <c r="C4" s="2">
         <v>10</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <v>120</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7">
         <v>116.7</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
       <c r="C5" s="5">
         <v>20</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>120</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7">
         <v>118.4</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B6" s="1"/>
       <c r="C6" s="2">
         <v>30</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>120</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7">
         <v>119.5</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
       <c r="C7" s="5">
         <v>40</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>120</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7">
         <v>122.8</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B8" s="1"/>
       <c r="C8" s="2">
         <v>50</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>120</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7">
         <v>125.9</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B9" s="1"/>
       <c r="C9" s="5">
         <v>60</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>120</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7">
         <v>124.2</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B10" s="1"/>
       <c r="C10" s="2">
         <v>70</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>120</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7">
         <v>123</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B11" s="1"/>
       <c r="C11" s="5">
         <v>80</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>120</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7">
         <v>124</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C12" s="2">
         <v>90</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>120</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="8">
         <v>130</v>
       </c>
@@ -3298,83 +3298,83 @@
       <c r="H12" s="8"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="7">
+        <v>120</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7">
+        <v>143.9</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C17" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="D17" s="7">
         <v>120</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6">
-        <v>143.9</v>
-      </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="6">
-        <v>120</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7">
         <v>139.4</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F17:G17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3383,168 +3383,168 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C690576D-BF07-4E9D-9403-3FC7897913C4}">
   <dimension ref="C3:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C3" s="6" t="s">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C4" s="6">
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C4" s="7">
         <v>120</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7">
         <v>115</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" s="6">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C5" s="7">
         <v>110</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7">
         <v>104.3</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="6">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C6" s="7">
         <v>100</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7">
         <v>92.6</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="6">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C7" s="7">
         <v>130</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7">
         <v>124.1</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="6">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C8" s="7">
         <v>140</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7">
         <v>134.6</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
